--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_LDLC ASVEL VILLEURBANNE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_LDLC ASVEL VILLEURBANNE.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>14.2887</v>
+        <v>34.4811</v>
       </c>
       <c r="E2" t="n">
-        <v>17.3073</v>
+        <v>29.5565</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0182</v>
+        <v>4.9247</v>
       </c>
       <c r="G2" t="n">
-        <v>25.5751</v>
+        <v>21.1286</v>
       </c>
       <c r="H2" t="n">
-        <v>10.4019</v>
+        <v>-17.0766</v>
       </c>
       <c r="I2" t="n">
-        <v>15.1731</v>
+        <v>38.2054</v>
       </c>
       <c r="J2" t="n">
-        <v>36.7757</v>
+        <v>53.8126</v>
       </c>
       <c r="K2" t="n">
-        <v>17.3447</v>
+        <v>7.6377</v>
       </c>
       <c r="L2" t="n">
-        <v>19.4312</v>
+        <v>46.1752</v>
       </c>
       <c r="M2" t="n">
-        <v>-11.2009</v>
+        <v>-32.684</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.942600000000001</v>
+        <v>-24.714</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.257899999999999</v>
+        <v>-7.9701</v>
       </c>
       <c r="P2" t="n">
-        <v>-21.3396</v>
+        <v>7.6543</v>
       </c>
       <c r="Q2" t="n">
-        <v>-43.1431</v>
+        <v>-49.8699</v>
       </c>
       <c r="R2" t="n">
-        <v>21.8039</v>
+        <v>57.5245</v>
       </c>
       <c r="S2" t="n">
-        <v>-10.7129</v>
+        <v>-1.6657</v>
       </c>
       <c r="T2" t="n">
-        <v>-7.5613</v>
+        <v>-2.3575</v>
       </c>
       <c r="U2" t="n">
-        <v>-3.1515</v>
+        <v>0.6916</v>
       </c>
       <c r="V2" t="n">
-        <v>20.7661</v>
+        <v>7.3636</v>
       </c>
       <c r="W2" t="n">
-        <v>31.2356</v>
+        <v>27.9705</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.4695</v>
+        <v>-20.6068</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12.102</v>
+        <v>22.1511</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0018</v>
+        <v>23.8455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1002000000000001</v>
+        <v>-1.6941</v>
       </c>
       <c r="G3" t="n">
-        <v>21.1286</v>
+        <v>25.5751</v>
       </c>
       <c r="H3" t="n">
-        <v>-17.0766</v>
+        <v>10.4019</v>
       </c>
       <c r="I3" t="n">
-        <v>38.2054</v>
+        <v>15.1731</v>
       </c>
       <c r="J3" t="n">
-        <v>53.8126</v>
+        <v>36.7757</v>
       </c>
       <c r="K3" t="n">
-        <v>7.6377</v>
+        <v>17.3447</v>
       </c>
       <c r="L3" t="n">
-        <v>46.1752</v>
+        <v>19.4312</v>
       </c>
       <c r="M3" t="n">
-        <v>-32.684</v>
+        <v>-11.2009</v>
       </c>
       <c r="N3" t="n">
-        <v>-24.714</v>
+        <v>-6.942600000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.9701</v>
+        <v>-4.257899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>7.6543</v>
+        <v>-21.3396</v>
       </c>
       <c r="Q3" t="n">
-        <v>-49.8699</v>
+        <v>-43.1431</v>
       </c>
       <c r="R3" t="n">
-        <v>57.5245</v>
+        <v>21.8039</v>
       </c>
       <c r="S3" t="n">
-        <v>-24.0448</v>
+        <v>-2.8503</v>
       </c>
       <c r="T3" t="n">
-        <v>-19.9118</v>
+        <v>-1.0229</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.1328</v>
+        <v>-1.8274</v>
       </c>
       <c r="V3" t="n">
-        <v>7.3636</v>
+        <v>20.7661</v>
       </c>
       <c r="W3" t="n">
-        <v>27.9705</v>
+        <v>31.2356</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.6068</v>
+        <v>-10.4695</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>11.7319</v>
+        <v>18.4887</v>
       </c>
       <c r="E4" t="n">
-        <v>9.0063</v>
+        <v>15.458</v>
       </c>
       <c r="F4" t="n">
-        <v>2.725900000000001</v>
+        <v>3.030899999999999</v>
       </c>
       <c r="G4" t="n">
         <v>2.6518</v>
@@ -766,13 +766,13 @@
         <v>28.9943</v>
       </c>
       <c r="S4" t="n">
-        <v>-9.503399999999999</v>
+        <v>-2.7465</v>
       </c>
       <c r="T4" t="n">
-        <v>-11.3341</v>
+        <v>-4.8823</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8305</v>
+        <v>2.1356</v>
       </c>
       <c r="V4" t="n">
         <v>22.2948</v>
@@ -799,13 +799,13 @@
         <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7838</v>
+        <v>-8.183800000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4017999999999997</v>
+        <v>-12.0634</v>
       </c>
       <c r="F5" t="n">
-        <v>4.184899999999999</v>
+        <v>3.8798</v>
       </c>
       <c r="G5" t="n">
         <v>3.517499999999999</v>
@@ -844,13 +844,13 @@
         <v>39.8962</v>
       </c>
       <c r="S5" t="n">
-        <v>17.9723</v>
+        <v>6.0056</v>
       </c>
       <c r="T5" t="n">
-        <v>16.3004</v>
+        <v>4.638800000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.672</v>
+        <v>1.3668</v>
       </c>
       <c r="V5" t="n">
         <v>-12.14</v>
@@ -877,13 +877,13 @@
         <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.835399999999999</v>
+        <v>-10.2527</v>
       </c>
       <c r="E6" t="n">
-        <v>3.185499999999999</v>
+        <v>-4.4854</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.0211</v>
+        <v>-5.767300000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-13.8874</v>
@@ -922,13 +922,13 @@
         <v>22.2678</v>
       </c>
       <c r="S6" t="n">
-        <v>13.2764</v>
+        <v>3.8592</v>
       </c>
       <c r="T6" t="n">
-        <v>8.379</v>
+        <v>0.7080999999999997</v>
       </c>
       <c r="U6" t="n">
-        <v>4.8976</v>
+        <v>3.1512</v>
       </c>
       <c r="V6" t="n">
         <v>-4.3996</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>-17.7741</v>
+        <v>-15.4799</v>
       </c>
       <c r="E7" t="n">
-        <v>-17.7776</v>
+        <v>-17.881</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003600000000000714</v>
+        <v>2.4013</v>
       </c>
       <c r="G7" t="n">
-        <v>-9.668800000000001</v>
+        <v>-17.7107</v>
       </c>
       <c r="H7" t="n">
-        <v>17.7667</v>
+        <v>-8.3255</v>
       </c>
       <c r="I7" t="n">
-        <v>-27.4358</v>
+        <v>-9.3849</v>
       </c>
       <c r="J7" t="n">
-        <v>16.0982</v>
+        <v>10.9399</v>
       </c>
       <c r="K7" t="n">
-        <v>30.4553</v>
+        <v>3.5107</v>
       </c>
       <c r="L7" t="n">
-        <v>-14.3572</v>
+        <v>7.4294</v>
       </c>
       <c r="M7" t="n">
-        <v>-25.7672</v>
+        <v>-28.6508</v>
       </c>
       <c r="N7" t="n">
-        <v>-12.6879</v>
+        <v>-11.8363</v>
       </c>
       <c r="O7" t="n">
-        <v>-13.079</v>
+        <v>-16.8144</v>
       </c>
       <c r="P7" t="n">
-        <v>2.087700000000001</v>
+        <v>1.855899999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-52.1895</v>
+        <v>-41.0557</v>
       </c>
       <c r="R7" t="n">
-        <v>54.2771</v>
+        <v>42.9117</v>
       </c>
       <c r="S7" t="n">
-        <v>11.9779</v>
+        <v>2.2229</v>
       </c>
       <c r="T7" t="n">
-        <v>10.5903</v>
+        <v>-0.9600999999999997</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3875</v>
+        <v>3.1833</v>
       </c>
       <c r="V7" t="n">
-        <v>-22.1706</v>
+        <v>-1.847300000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>7.7229</v>
+        <v>13.1946</v>
       </c>
       <c r="X7" t="n">
-        <v>-29.8934</v>
+        <v>-15.0419</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" t="n">
-        <v>-19.4899</v>
+        <v>-15.8847</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.2881</v>
+        <v>-11.2764</v>
       </c>
       <c r="F8" t="n">
-        <v>-15.2014</v>
+        <v>-4.6087</v>
       </c>
       <c r="G8" t="n">
-        <v>-22.6519</v>
+        <v>-43.8994</v>
       </c>
       <c r="H8" t="n">
-        <v>-22.0588</v>
+        <v>-15.1347</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5933999999999998</v>
+        <v>-28.7651</v>
       </c>
       <c r="J8" t="n">
-        <v>3.975700000000001</v>
+        <v>-13.1492</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.1393</v>
+        <v>7.498</v>
       </c>
       <c r="L8" t="n">
-        <v>11.115</v>
+        <v>-20.6477</v>
       </c>
       <c r="M8" t="n">
-        <v>-26.6278</v>
+        <v>-30.7503</v>
       </c>
       <c r="N8" t="n">
-        <v>-14.9192</v>
+        <v>-22.633</v>
       </c>
       <c r="O8" t="n">
-        <v>-11.7085</v>
+        <v>-8.117599999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.582000000000001</v>
+        <v>42.6794</v>
       </c>
       <c r="Q8" t="n">
-        <v>-42.4478</v>
+        <v>-14.3815</v>
       </c>
       <c r="R8" t="n">
-        <v>33.8658</v>
+        <v>57.0609</v>
       </c>
       <c r="S8" t="n">
-        <v>20.4947</v>
+        <v>3.687</v>
       </c>
       <c r="T8" t="n">
-        <v>16.9526</v>
+        <v>-0.1129000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5421</v>
+        <v>3.7996</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.750399999999999</v>
+        <v>-18.3518</v>
       </c>
       <c r="W8" t="n">
-        <v>17.2307</v>
+        <v>16.3666</v>
       </c>
       <c r="X8" t="n">
-        <v>-25.9814</v>
+        <v>-34.7184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>-22.2796</v>
+        <v>-23.4387</v>
       </c>
       <c r="E9" t="n">
-        <v>-23.5895</v>
+        <v>-13.6237</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3102</v>
+        <v>-9.814499999999997</v>
       </c>
       <c r="G9" t="n">
-        <v>-17.7107</v>
+        <v>-29.3263</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.3255</v>
+        <v>-15.1865</v>
       </c>
       <c r="I9" t="n">
-        <v>-9.3849</v>
+        <v>-14.1395</v>
       </c>
       <c r="J9" t="n">
-        <v>10.9399</v>
+        <v>6.397600000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5107</v>
+        <v>7.1831</v>
       </c>
       <c r="L9" t="n">
-        <v>7.4294</v>
+        <v>-0.7851999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-28.6508</v>
+        <v>-35.7237</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.8363</v>
+        <v>-22.3696</v>
       </c>
       <c r="O9" t="n">
-        <v>-16.8144</v>
+        <v>-13.3543</v>
       </c>
       <c r="P9" t="n">
-        <v>1.855899999999999</v>
+        <v>20.4119</v>
       </c>
       <c r="Q9" t="n">
-        <v>-41.0557</v>
+        <v>-23.6597</v>
       </c>
       <c r="R9" t="n">
-        <v>42.9117</v>
+        <v>44.0713</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.5772</v>
+        <v>-1.9897</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.6685</v>
+        <v>-1.3603</v>
       </c>
       <c r="U9" t="n">
-        <v>2.0918</v>
+        <v>-0.6293000000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.847300000000001</v>
+        <v>-12.5343</v>
       </c>
       <c r="W9" t="n">
-        <v>13.1946</v>
+        <v>4.9978</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.0419</v>
+        <v>-17.5321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>-23.0859</v>
+        <v>-25.4957</v>
       </c>
       <c r="E10" t="n">
-        <v>-15.8248</v>
+        <v>-24.7451</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.2608</v>
+        <v>-0.7507999999999989</v>
       </c>
       <c r="G10" t="n">
-        <v>-43.8994</v>
+        <v>-9.668800000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-15.1347</v>
+        <v>17.7667</v>
       </c>
       <c r="I10" t="n">
-        <v>-28.7651</v>
+        <v>-27.4358</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.1492</v>
+        <v>16.0982</v>
       </c>
       <c r="K10" t="n">
-        <v>7.498</v>
+        <v>30.4553</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.6477</v>
+        <v>-14.3572</v>
       </c>
       <c r="M10" t="n">
-        <v>-30.7503</v>
+        <v>-25.7672</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.633</v>
+        <v>-12.6879</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.117599999999999</v>
+        <v>-13.079</v>
       </c>
       <c r="P10" t="n">
-        <v>42.6794</v>
+        <v>2.087700000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-14.3815</v>
+        <v>-52.1895</v>
       </c>
       <c r="R10" t="n">
-        <v>57.0609</v>
+        <v>54.2771</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.5137</v>
+        <v>4.2564</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.661300000000001</v>
+        <v>3.6232</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1474</v>
+        <v>0.6331999999999998</v>
       </c>
       <c r="V10" t="n">
-        <v>-18.3518</v>
+        <v>-22.1706</v>
       </c>
       <c r="W10" t="n">
-        <v>16.3666</v>
+        <v>7.7229</v>
       </c>
       <c r="X10" t="n">
-        <v>-34.7184</v>
+        <v>-29.8934</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>E. JACKSON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>-29.7345</v>
+        <v>-25.952</v>
       </c>
       <c r="E11" t="n">
-        <v>-24.6551</v>
+        <v>-15.4017</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0794</v>
+        <v>-10.5508</v>
       </c>
       <c r="G11" t="n">
-        <v>-23.2474</v>
+        <v>-11.9069</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.4573</v>
+        <v>-19.097</v>
       </c>
       <c r="I11" t="n">
-        <v>-8.790099999999999</v>
+        <v>7.1896</v>
       </c>
       <c r="J11" t="n">
-        <v>-19.0434</v>
+        <v>4.770500000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-11.2295</v>
+        <v>-6.6838</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.8137</v>
+        <v>11.4544</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.204</v>
+        <v>-16.6776</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.2279</v>
+        <v>-12.413</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9762000000000002</v>
+        <v>-4.2646</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1599</v>
+        <v>-3.943</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.9741</v>
+        <v>-24.5874</v>
       </c>
       <c r="R11" t="n">
-        <v>8.814299999999999</v>
+        <v>20.6441</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.4693</v>
+        <v>-1.2412</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8188</v>
+        <v>-0.3305</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.6507</v>
+        <v>-0.9103000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1417999999999999</v>
+        <v>-8.8612</v>
       </c>
       <c r="W11" t="n">
-        <v>6.1807</v>
+        <v>4.7453</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.0389</v>
+        <v>-13.6065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ATAMNA</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>-31.1736</v>
+        <v>-26.3385</v>
       </c>
       <c r="E12" t="n">
-        <v>-30.6201</v>
+        <v>-27.3154</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5536999999999996</v>
+        <v>0.976699999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-26.006</v>
+        <v>12.1873</v>
       </c>
       <c r="H12" t="n">
-        <v>-14.1372</v>
+        <v>-7.4056</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.8689</v>
+        <v>19.5926</v>
       </c>
       <c r="J12" t="n">
-        <v>-20.9894</v>
+        <v>39.3397</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.099399999999999</v>
+        <v>12.0399</v>
       </c>
       <c r="L12" t="n">
-        <v>-11.8898</v>
+        <v>27.2998</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.017</v>
+        <v>-27.1523</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.0377</v>
+        <v>-19.4456</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02089999999999992</v>
+        <v>-7.7071</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6239</v>
+        <v>-45.2305</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.8298</v>
+        <v>-77.7042</v>
       </c>
       <c r="R12" t="n">
-        <v>13.4536</v>
+        <v>32.4736</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3992</v>
+        <v>-2.1564</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2294</v>
+        <v>-5.2384</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.17</v>
+        <v>3.082</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.3921</v>
+        <v>8.8612</v>
       </c>
       <c r="W12" t="n">
-        <v>2.428</v>
+        <v>16.287</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.8201</v>
+        <v>-7.4258</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-31.7465</v>
+        <v>-26.345</v>
       </c>
       <c r="E13" t="n">
-        <v>-25.7387</v>
+        <v>-23.0159</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.007700000000001</v>
+        <v>-3.3294</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.4163</v>
+        <v>-23.2474</v>
       </c>
       <c r="H13" t="n">
-        <v>-25.2155</v>
+        <v>-14.4573</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>-8.790099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9083</v>
+        <v>-19.0434</v>
       </c>
       <c r="K13" t="n">
-        <v>-10.5551</v>
+        <v>-11.2295</v>
       </c>
       <c r="L13" t="n">
-        <v>12.4631</v>
+        <v>-7.8137</v>
       </c>
       <c r="M13" t="n">
-        <v>-23.3246</v>
+        <v>-4.204</v>
       </c>
       <c r="N13" t="n">
-        <v>-14.6608</v>
+        <v>-3.2279</v>
       </c>
       <c r="O13" t="n">
-        <v>-8.663499999999999</v>
+        <v>-0.9762000000000002</v>
       </c>
       <c r="P13" t="n">
-        <v>-6.9589</v>
+        <v>-1.1599</v>
       </c>
       <c r="Q13" t="n">
-        <v>-47.5506</v>
+        <v>-9.9741</v>
       </c>
       <c r="R13" t="n">
-        <v>40.592</v>
+        <v>8.814299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>22.1707</v>
+        <v>-2.0796</v>
       </c>
       <c r="T13" t="n">
-        <v>17.4128</v>
+        <v>-0.1793</v>
       </c>
       <c r="U13" t="n">
-        <v>4.7576</v>
+        <v>-1.9004</v>
       </c>
       <c r="V13" t="n">
-        <v>-25.5425</v>
+        <v>0.1417999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>2.4902</v>
+        <v>6.1807</v>
       </c>
       <c r="X13" t="n">
-        <v>-28.0327</v>
+        <v>-6.0389</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>A. ATAMNA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>-32.0662</v>
+        <v>-29.4094</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.5331</v>
+        <v>-30.235</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.5328</v>
+        <v>0.8258</v>
       </c>
       <c r="G14" t="n">
-        <v>-29.3263</v>
+        <v>-26.006</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.1865</v>
+        <v>-14.1372</v>
       </c>
       <c r="I14" t="n">
-        <v>-14.1395</v>
+        <v>-11.8689</v>
       </c>
       <c r="J14" t="n">
-        <v>6.397600000000001</v>
+        <v>-20.9894</v>
       </c>
       <c r="K14" t="n">
-        <v>7.1831</v>
+        <v>-9.099399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7851999999999999</v>
+        <v>-11.8898</v>
       </c>
       <c r="M14" t="n">
-        <v>-35.7237</v>
+        <v>-5.017</v>
       </c>
       <c r="N14" t="n">
-        <v>-22.3696</v>
+        <v>-5.0377</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.3543</v>
+        <v>0.02089999999999992</v>
       </c>
       <c r="P14" t="n">
-        <v>20.4119</v>
+        <v>1.6239</v>
       </c>
       <c r="Q14" t="n">
-        <v>-23.6597</v>
+        <v>-11.8298</v>
       </c>
       <c r="R14" t="n">
-        <v>44.0713</v>
+        <v>13.4536</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.617</v>
+        <v>0.3652</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.2694</v>
+        <v>0.1556000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.3478</v>
+        <v>0.2092999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-12.5343</v>
+        <v>-5.3921</v>
       </c>
       <c r="W14" t="n">
-        <v>4.9978</v>
+        <v>2.428</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.5321</v>
+        <v>-7.8201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. JACKSON</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>-36.0459</v>
+        <v>-30.5605</v>
       </c>
       <c r="E15" t="n">
-        <v>-22.1639</v>
+        <v>-17.6645</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.8817</v>
+        <v>-12.8961</v>
       </c>
       <c r="G15" t="n">
-        <v>-11.9069</v>
+        <v>-22.6519</v>
       </c>
       <c r="H15" t="n">
-        <v>-19.097</v>
+        <v>-22.0588</v>
       </c>
       <c r="I15" t="n">
-        <v>7.1896</v>
+        <v>-0.5933999999999998</v>
       </c>
       <c r="J15" t="n">
-        <v>4.770500000000001</v>
+        <v>3.975700000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.6838</v>
+        <v>-7.1393</v>
       </c>
       <c r="L15" t="n">
-        <v>11.4544</v>
+        <v>11.115</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.6776</v>
+        <v>-26.6278</v>
       </c>
       <c r="N15" t="n">
-        <v>-12.413</v>
+        <v>-14.9192</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.2646</v>
+        <v>-11.7085</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.943</v>
+        <v>-8.582000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-24.5874</v>
+        <v>-42.4478</v>
       </c>
       <c r="R15" t="n">
-        <v>20.6441</v>
+        <v>33.8658</v>
       </c>
       <c r="S15" t="n">
-        <v>-11.3343</v>
+        <v>9.4237</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.0932</v>
+        <v>3.5762</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.2416</v>
+        <v>5.8474</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.8612</v>
+        <v>-8.750399999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>4.7453</v>
+        <v>17.2307</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.6065</v>
+        <v>-25.9814</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>-44.478</v>
+        <v>-41.4601</v>
       </c>
       <c r="E16" t="n">
-        <v>-40.7772</v>
+        <v>-38.0152</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.701</v>
+        <v>-3.445000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>12.1873</v>
+        <v>-47.5635</v>
       </c>
       <c r="H16" t="n">
-        <v>-7.4056</v>
+        <v>-27.9177</v>
       </c>
       <c r="I16" t="n">
-        <v>19.5926</v>
+        <v>-19.6457</v>
       </c>
       <c r="J16" t="n">
-        <v>39.3397</v>
+        <v>-19.9567</v>
       </c>
       <c r="K16" t="n">
-        <v>12.0399</v>
+        <v>-9.5534</v>
       </c>
       <c r="L16" t="n">
-        <v>27.2998</v>
+        <v>-10.4032</v>
       </c>
       <c r="M16" t="n">
-        <v>-27.1523</v>
+        <v>-27.6068</v>
       </c>
       <c r="N16" t="n">
-        <v>-19.4456</v>
+        <v>-18.3644</v>
       </c>
       <c r="O16" t="n">
-        <v>-7.7071</v>
+        <v>-9.242099999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-45.2305</v>
+        <v>13.6854</v>
       </c>
       <c r="Q16" t="n">
-        <v>-77.7042</v>
+        <v>-25.5151</v>
       </c>
       <c r="R16" t="n">
-        <v>32.4736</v>
+        <v>39.2003</v>
       </c>
       <c r="S16" t="n">
-        <v>-20.296</v>
+        <v>-5.2334</v>
       </c>
       <c r="T16" t="n">
-        <v>-18.7004</v>
+        <v>-1.2943</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.5957</v>
+        <v>-3.9392</v>
       </c>
       <c r="V16" t="n">
-        <v>8.8612</v>
+        <v>-2.3484</v>
       </c>
       <c r="W16" t="n">
-        <v>16.287</v>
+        <v>8.750500000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.4258</v>
+        <v>-11.0989</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>-48.2178</v>
+        <v>-45.4424</v>
       </c>
       <c r="E17" t="n">
-        <v>-39.9299</v>
+        <v>-37.1331</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.288399999999999</v>
+        <v>-8.3093</v>
       </c>
       <c r="G17" t="n">
-        <v>-47.5635</v>
+        <v>-21.4163</v>
       </c>
       <c r="H17" t="n">
-        <v>-27.9177</v>
+        <v>-25.2155</v>
       </c>
       <c r="I17" t="n">
-        <v>-19.6457</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
-        <v>-19.9567</v>
+        <v>1.9083</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.5534</v>
+        <v>-10.5551</v>
       </c>
       <c r="L17" t="n">
-        <v>-10.4032</v>
+        <v>12.4631</v>
       </c>
       <c r="M17" t="n">
-        <v>-27.6068</v>
+        <v>-23.3246</v>
       </c>
       <c r="N17" t="n">
-        <v>-18.3644</v>
+        <v>-14.6608</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.242099999999999</v>
+        <v>-8.663499999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>13.6854</v>
+        <v>-6.9589</v>
       </c>
       <c r="Q17" t="n">
-        <v>-25.5151</v>
+        <v>-47.5506</v>
       </c>
       <c r="R17" t="n">
-        <v>39.2003</v>
+        <v>40.592</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.9913</v>
+        <v>8.4748</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.2087</v>
+        <v>6.0182</v>
       </c>
       <c r="U17" t="n">
-        <v>-8.782400000000001</v>
+        <v>2.4565</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3484</v>
+        <v>-25.5425</v>
       </c>
       <c r="W17" t="n">
-        <v>8.750500000000001</v>
+        <v>2.4902</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.0989</v>
+        <v>-28.0327</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>-295.0210000000001</v>
+        <v>-249.1225</v>
       </c>
       <c r="E18" t="n">
-        <v>-220.7989</v>
+        <v>-203.9958</v>
       </c>
       <c r="F18" t="n">
-        <v>-74.2214</v>
+        <v>-45.1268</v>
       </c>
       <c r="G18" t="n">
         <v>-202.2243</v>
@@ -1837,7 +1837,7 @@
         <v>66.4503</v>
       </c>
       <c r="L18" t="n">
-        <v>80.74700000000001</v>
+        <v>80.747</v>
       </c>
       <c r="M18" t="n">
         <v>-349.4225</v>
@@ -1849,7 +1849,7 @@
         <v>-122.8115</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.318299999999997</v>
+        <v>-2.318299999999979</v>
       </c>
       <c r="Q18" t="n">
         <v>-560.1692</v>
@@ -1858,16 +1858,16 @@
         <v>557.8514</v>
       </c>
       <c r="S18" t="n">
-        <v>-27.5671</v>
+        <v>18.332</v>
       </c>
       <c r="T18" t="n">
-        <v>-15.8218</v>
+        <v>0.981600000000002</v>
       </c>
       <c r="U18" t="n">
-        <v>-11.746</v>
+        <v>17.3499</v>
       </c>
       <c r="V18" t="n">
-        <v>-62.9107</v>
+        <v>-62.91070000000001</v>
       </c>
       <c r="W18" t="n">
         <v>207.9874</v>
